--- a/experiment_results/combined_sweep/rtt_bursts_S4_atk10pct_wu300000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S4_atk10pct_wu300000.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2016592</t>
+          <t>1382924</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2836320</t>
+          <t>1453506</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3114596</t>
+          <t>1661200</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3936395</t>
+          <t>2275306</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5132069</t>
+          <t>2856874</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6386897</t>
+          <t>3530133</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7612586</t>
+          <t>4082563</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8755207</t>
+          <t>4672754</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9678281</t>
+          <t>5005637</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10169750</t>
+          <t>5164222</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10559309</t>
+          <t>5395197</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10908437</t>
+          <t>5513350</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11235358</t>
+          <t>5722117</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11438799</t>
+          <t>5716792</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>11418351</t>
+          <t>5701669</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11402663</t>
+          <t>5701104</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11402098</t>
+          <t>5701104</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
